--- a/Experiments/DBCV_DGCNN.xlsx
+++ b/Experiments/DBCV_DGCNN.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9396DEC8-F684-4572-8981-08121065E940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7184DCCF-BCA0-4776-B09F-C50095616E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="95">
   <si>
     <t>TEST DATASET(1024)</t>
   </si>
@@ -211,6 +214,117 @@
   </si>
   <si>
     <t>162.210 secs</t>
+  </si>
+  <si>
+    <t>TEST DATASET(256)</t>
+  </si>
+  <si>
+    <t>(k=64)</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>-0.114</t>
+  </si>
+  <si>
+    <t>0.171</t>
+  </si>
+  <si>
+    <t>-0.151</t>
+  </si>
+  <si>
+    <t>-0.078</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>-0.001</t>
+  </si>
+  <si>
+    <t>TEST DATASET(128)</t>
+  </si>
+  <si>
+    <t>(k=32)</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>-0.120</t>
+  </si>
+  <si>
+    <t>0.131</t>
+  </si>
+  <si>
+    <t>-0.116</t>
+  </si>
+  <si>
+    <t>-0.108</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>-0.099</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>-0.111</t>
+  </si>
+  <si>
+    <t>0.137</t>
+  </si>
+  <si>
+    <t>-0.074</t>
+  </si>
+  <si>
+    <t>-0.090</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>-0.104</t>
+  </si>
+  <si>
+    <t>0.225</t>
+  </si>
+  <si>
+    <t>0.182</t>
+  </si>
+  <si>
+    <t>-0.054</t>
+  </si>
+  <si>
+    <t>0.213</t>
+  </si>
+  <si>
+    <t>-0.202</t>
+  </si>
+  <si>
+    <t>-0.129</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>-0.17</t>
+  </si>
+  <si>
+    <t>0.550</t>
+  </si>
+  <si>
+    <t>-0.409</t>
   </si>
 </sst>
 </file>
@@ -299,8 +413,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,23 +752,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC741B33-8327-42E5-99D2-10620C98A133}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
-    <col min="9" max="9" width="13.6328125" customWidth="1"/>
-    <col min="10" max="10" width="16.7265625" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" customWidth="1"/>
-    <col min="13" max="13" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -661,21 +777,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -719,7 +835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -752,7 +868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -766,14 +882,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -806,7 +922,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -839,14 +955,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -854,7 +970,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -887,26 +1003,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
-        <v>1000</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="10">
-        <v>2</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="6"/>
@@ -914,14 +1027,14 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -938,7 +1051,7 @@
       </c>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
@@ -946,7 +1059,7 @@
       <c r="I17" s="1"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -963,7 +1076,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -971,7 +1084,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -988,24 +1101,24 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9" t="s">
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>31</v>
@@ -1038,7 +1151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -1084,25 +1197,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12FA993-8E8A-42F8-A34C-BCBF8AAE8AD1}">
-  <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.90625" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.81640625" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" customWidth="1"/>
-    <col min="13" max="13" width="25.90625" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -1111,21 +1224,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1169,7 +1282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -1197,7 +1310,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1211,14 +1324,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -1246,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -1274,14 +1387,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -1289,7 +1402,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -1317,26 +1430,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
-        <v>1000</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="10">
-        <v>2</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="6"/>
@@ -1344,14 +1454,14 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -1368,7 +1478,7 @@
       </c>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
@@ -1376,7 +1486,7 @@
       <c r="I17" s="1"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -1393,7 +1503,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -1401,7 +1511,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -1418,24 +1528,24 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9" t="s">
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>31</v>
@@ -1468,7 +1578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -1501,6 +1611,575 @@
       </c>
       <c r="K25" s="1" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="G29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" t="s">
+        <v>12</v>
+      </c>
+      <c r="M32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="D33" s="1"/>
+      <c r="F33" s="3">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>7034</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="3">
+        <v>591</v>
+      </c>
+      <c r="J33" t="s">
+        <v>85</v>
+      </c>
+      <c r="K33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L33" s="1">
+        <v>3596855</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="F35" s="1"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="D36" s="1"/>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>6666</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="3">
+        <v>175</v>
+      </c>
+      <c r="J36" t="s">
+        <v>91</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L36" s="1">
+        <v>399792</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="D37" s="1"/>
+      <c r="F37" s="3">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>6511</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="3">
+        <v>175</v>
+      </c>
+      <c r="J37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="1">
+        <v>409159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="F38" s="1"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="F39" s="1"/>
+      <c r="I39" s="3"/>
+      <c r="K39" s="7"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>2000</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="D40" s="1"/>
+      <c r="F40" s="3">
+        <v>2</v>
+      </c>
+      <c r="G40" s="1">
+        <v>6730</v>
+      </c>
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3">
+        <v>175</v>
+      </c>
+      <c r="J40" s="1">
+        <v>26729</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L40" s="1">
+        <v>410735</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" t="s">
+        <v>34</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="1">
+        <v>591</v>
+      </c>
+      <c r="D45">
+        <v>193</v>
+      </c>
+      <c r="E45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45">
+        <v>223</v>
+      </c>
+      <c r="I45" s="1">
+        <v>73</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K45" s="1">
+        <v>604703</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="G49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" t="s">
+        <v>11</v>
+      </c>
+      <c r="L52" t="s">
+        <v>12</v>
+      </c>
+      <c r="M52" t="s">
+        <v>13</v>
+      </c>
+      <c r="N52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="D53" s="1"/>
+      <c r="F53" s="3">
+        <v>2</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="L53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="F55" s="1"/>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="D56" s="1"/>
+      <c r="F56" s="3">
+        <v>2</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="3">
+        <v>175</v>
+      </c>
+      <c r="K56" s="8"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="D57" s="1"/>
+      <c r="F57" s="3">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1">
+        <v>18025</v>
+      </c>
+      <c r="H57" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="3">
+        <v>175</v>
+      </c>
+      <c r="J57" t="s">
+        <v>93</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L57" s="1">
+        <v>2696609</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="F58" s="1"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="F59" s="1"/>
+      <c r="I59" s="3"/>
+      <c r="K59" s="7"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="D60" s="1"/>
+      <c r="F60" s="3">
+        <v>2</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="3">
+        <v>175</v>
+      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="1"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" t="s">
+        <v>31</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I64" t="s">
+        <v>34</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="1">
+        <v>591</v>
+      </c>
+      <c r="D65">
+        <v>193</v>
+      </c>
+      <c r="E65" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" t="s">
+        <v>51</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65">
+        <v>223</v>
+      </c>
+      <c r="I65" s="1">
+        <v>73</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K65" s="1">
+        <v>604703</v>
       </c>
     </row>
   </sheetData>
@@ -1510,4 +2189,1106 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E652DF1D-93D7-4843-A898-B564AEFAAE58}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3374</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>278</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="1">
+        <v>240169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3722</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="1">
+        <v>92631</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3673</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="1">
+        <v>103629</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3579</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6933</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="1">
+        <v>105700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1">
+        <v>278</v>
+      </c>
+      <c r="D17">
+        <v>141</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="1">
+        <v>240169</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <v>116</v>
+      </c>
+      <c r="I17" s="1">
+        <v>46</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="1">
+        <v>62288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D727ADA0-5113-499F-B7CF-72723C82F907}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="36.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3498</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>289</v>
+      </c>
+      <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="1">
+        <v>250010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3590</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="1">
+        <v>104450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3839</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" s="1">
+        <v>106311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3559</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6662</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="1">
+        <v>103972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1">
+        <v>289</v>
+      </c>
+      <c r="D17">
+        <v>146</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="1">
+        <v>250010</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>127</v>
+      </c>
+      <c r="I17" s="1">
+        <v>52</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" s="1">
+        <v>65277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C70911A-DBE7-4141-B687-67DF4C8C8D7B}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" customWidth="1"/>
+    <col min="10" max="11" width="17.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="32.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3430</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>289</v>
+      </c>
+      <c r="J5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="1">
+        <v>253259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3298</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="1">
+        <v>104248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3572</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="1">
+        <v>107411</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3384</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6879</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="1">
+        <v>105169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1">
+        <v>289</v>
+      </c>
+      <c r="D17">
+        <v>146</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="1">
+        <v>253259</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>116</v>
+      </c>
+      <c r="I17" s="1">
+        <v>40</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="1">
+        <v>58922</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Experiments/DBCV_DGCNN.xlsx
+++ b/Experiments/DBCV_DGCNN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Downloads\thesis_documentation\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Documents\GIT\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7184DCCF-BCA0-4776-B09F-C50095616E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4973FE3-7D97-432D-A4A4-C477D2D0ED07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="8" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="137">
   <si>
     <t>TEST DATASET(1024)</t>
   </si>
@@ -325,6 +329,132 @@
   </si>
   <si>
     <t>-0.409</t>
+  </si>
+  <si>
+    <t>TEST DATASET(64)</t>
+  </si>
+  <si>
+    <t>0.647</t>
+  </si>
+  <si>
+    <t>0.185</t>
+  </si>
+  <si>
+    <t>-0.026</t>
+  </si>
+  <si>
+    <t>Level 3</t>
+  </si>
+  <si>
+    <t>-0.205</t>
+  </si>
+  <si>
+    <t>TEST DATASET(32)</t>
+  </si>
+  <si>
+    <t>(k=16)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>0.179</t>
+  </si>
+  <si>
+    <t>-0.138</t>
+  </si>
+  <si>
+    <t>0.304</t>
+  </si>
+  <si>
+    <t>-0.098</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>-0.110</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>-0.112</t>
+  </si>
+  <si>
+    <t>0.126</t>
+  </si>
+  <si>
+    <t>-0.132</t>
+  </si>
+  <si>
+    <t>-0.095</t>
+  </si>
+  <si>
+    <t>TEST DATASET(16)</t>
+  </si>
+  <si>
+    <t>(k=8)</t>
+  </si>
+  <si>
+    <t>TEST DATASET(8)</t>
+  </si>
+  <si>
+    <t>(k=4 )</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>-0.086</t>
+  </si>
+  <si>
+    <t>102-742</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>0.141</t>
+  </si>
+  <si>
+    <t>-0.107</t>
+  </si>
+  <si>
+    <t>-0.087</t>
+  </si>
+  <si>
+    <t>TEST DATASET(4)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>-0.082</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>-0.123</t>
+  </si>
+  <si>
+    <t>0.144</t>
+  </si>
+  <si>
+    <t>-0.135</t>
+  </si>
+  <si>
+    <t>-0.059</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>-0.100</t>
   </si>
 </sst>
 </file>
@@ -752,23 +882,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC741B33-8327-42E5-99D2-10620C98A133}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="27.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="16.7265625" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" customWidth="1"/>
+    <col min="13" max="13" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -777,21 +907,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -835,7 +965,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -868,7 +998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -882,14 +1012,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -922,7 +1052,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -955,14 +1085,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -970,7 +1100,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -1003,14 +1133,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1000</v>
       </c>
@@ -1027,14 +1157,14 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -1051,7 +1181,7 @@
       </c>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
@@ -1059,7 +1189,7 @@
       <c r="I17" s="1"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -1076,7 +1206,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -1084,7 +1214,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -1101,7 +1231,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="11" t="s">
         <v>29</v>
@@ -1118,7 +1248,7 @@
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>31</v>
@@ -1151,7 +1281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -1192,30 +1322,34 @@
     <mergeCell ref="G23:K23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12FA993-8E8A-42F8-A34C-BCBF8AAE8AD1}">
-  <dimension ref="A1:N65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P65"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" customWidth="1"/>
+    <col min="12" max="12" width="13.7265625" customWidth="1"/>
+    <col min="13" max="13" width="25.81640625" customWidth="1"/>
+    <col min="14" max="14" width="16.453125" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -1224,21 +1358,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1282,7 +1416,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -1310,7 +1444,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1324,14 +1458,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -1359,7 +1493,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -1387,14 +1521,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -1402,7 +1536,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -1430,14 +1564,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1000</v>
       </c>
@@ -1454,14 +1588,14 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -1478,7 +1612,7 @@
       </c>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
@@ -1486,7 +1620,7 @@
       <c r="I17" s="1"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -1503,7 +1637,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -1511,7 +1645,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -1528,7 +1662,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="11" t="s">
         <v>29</v>
@@ -1545,7 +1679,7 @@
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>31</v>
@@ -1578,7 +1712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -1613,7 +1747,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="C29" s="1"/>
       <c r="E29" s="1"/>
@@ -1622,21 +1756,21 @@
       </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="C30" s="1"/>
       <c r="E30" s="1"/>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="C31" s="1"/>
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -1680,7 +1814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>2000</v>
       </c>
@@ -1708,7 +1842,7 @@
         <v>3596855</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
@@ -1722,14 +1856,14 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="D35" s="3"/>
       <c r="F35" s="1"/>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>2000</v>
       </c>
@@ -1757,7 +1891,7 @@
         <v>399792</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>2000</v>
       </c>
@@ -1785,14 +1919,14 @@
         <v>409159</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="D38" s="3"/>
       <c r="F38" s="1"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="D39" s="3"/>
@@ -1800,7 +1934,7 @@
       <c r="I39" s="3"/>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>2000</v>
       </c>
@@ -1828,7 +1962,7 @@
         <v>410735</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="9" t="s">
         <v>29</v>
@@ -1845,7 +1979,7 @@
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" t="s">
         <v>31</v>
@@ -1878,7 +2012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>1000</v>
       </c>
@@ -1913,7 +2047,7 @@
         <v>604703</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="C49" s="1"/>
       <c r="E49" s="1"/>
@@ -1922,21 +2056,21 @@
       </c>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="C50" s="1"/>
       <c r="E50" s="1"/>
       <c r="G50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="C51" s="1"/>
       <c r="E51" s="1"/>
       <c r="G51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>1</v>
       </c>
@@ -1980,7 +2114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>5000</v>
       </c>
@@ -1989,14 +2123,26 @@
       <c r="F53" s="3">
         <v>2</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1">
+        <v>17516</v>
+      </c>
       <c r="H53" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="3"/>
-      <c r="L53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I53" s="3">
+        <v>1486</v>
+      </c>
+      <c r="J53" t="s">
+        <v>96</v>
+      </c>
+      <c r="K53" t="s">
+        <v>97</v>
+      </c>
+      <c r="L53" s="1">
+        <v>120280203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
@@ -2010,14 +2156,14 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="D55" s="3"/>
       <c r="F55" s="1"/>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>5000</v>
       </c>
@@ -2034,7 +2180,7 @@
       </c>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>5000</v>
       </c>
@@ -2062,14 +2208,14 @@
         <v>2696609</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="D58" s="3"/>
       <c r="F58" s="1"/>
       <c r="I58" s="3"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="D59" s="3"/>
@@ -2077,7 +2223,7 @@
       <c r="I59" s="3"/>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>5000</v>
       </c>
@@ -2097,7 +2243,7 @@
       <c r="K60" s="8"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="9" t="s">
         <v>29</v>
@@ -2113,8 +2259,15 @@
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L63" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" t="s">
         <v>31</v>
@@ -2146,40 +2299,70 @@
       <c r="K64" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L64" t="s">
+        <v>31</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N64" t="s">
+        <v>34</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>1000</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="1">
-        <v>591</v>
+      <c r="C65" s="3">
+        <v>1486</v>
       </c>
       <c r="D65">
-        <v>193</v>
+        <v>510</v>
       </c>
       <c r="E65" t="s">
-        <v>50</v>
-      </c>
-      <c r="F65" t="s">
-        <v>51</v>
+        <v>97</v>
+      </c>
+      <c r="F65" s="1">
+        <v>120280203</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H65">
-        <v>223</v>
+        <v>609</v>
       </c>
       <c r="I65" s="1">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K65" s="1">
-        <v>604703</v>
+        <v>20460755</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M65">
+        <v>265</v>
+      </c>
+      <c r="N65" s="1">
+        <v>106</v>
+      </c>
+      <c r="O65" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="P65" s="1">
+        <v>4595876</v>
       </c>
     </row>
   </sheetData>
@@ -2188,30 +2371,31 @@
     <mergeCell ref="G23:K23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E652DF1D-93D7-4843-A898-B564AEFAAE58}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.54296875" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" customWidth="1"/>
     <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -2223,21 +2407,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2281,7 +2465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -2309,7 +2493,7 @@
         <v>240169</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -2323,14 +2507,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -2358,7 +2542,7 @@
         <v>92631</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -2386,14 +2570,14 @@
         <v>103629</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -2401,7 +2585,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -2429,14 +2613,14 @@
         <v>105700</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -2446,7 +2630,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -2463,7 +2647,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -2496,7 +2680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -2531,7 +2715,7 @@
         <v>62288</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -2539,7 +2723,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -2547,7 +2731,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="D20" s="1"/>
@@ -2568,24 +2752,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D727ADA0-5113-499F-B7CF-72723C82F907}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" customWidth="1"/>
-    <col min="13" max="13" width="36.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" customWidth="1"/>
+    <col min="7" max="7" width="21.26953125" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" customWidth="1"/>
+    <col min="13" max="13" width="36.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -2597,21 +2781,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2655,7 +2839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -2683,7 +2867,7 @@
         <v>250010</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -2697,14 +2881,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -2732,7 +2916,7 @@
         <v>104450</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -2760,14 +2944,14 @@
         <v>106311</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -2775,7 +2959,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -2803,14 +2987,14 @@
         <v>103972</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -2820,7 +3004,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -2837,7 +3021,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -2870,7 +3054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -2905,7 +3089,7 @@
         <v>65277</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -2913,7 +3097,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -2927,54 +3111,55 @@
     <mergeCell ref="G15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C70911A-DBE7-4141-B687-67DF4C8C8D7B}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" customWidth="1"/>
-    <col min="10" max="11" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="9" max="9" width="18.1796875" customWidth="1"/>
+    <col min="10" max="11" width="17.54296875" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="32.28515625" customWidth="1"/>
+    <col min="13" max="13" width="32.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>68</v>
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3018,7 +3203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -3046,7 +3231,7 @@
         <v>253259</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -3060,14 +3245,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -3095,7 +3280,7 @@
         <v>104248</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -3123,14 +3308,14 @@
         <v>107411</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -3138,7 +3323,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -3166,14 +3351,14 @@
         <v>105169</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -3183,7 +3368,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -3200,7 +3385,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -3233,7 +3418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -3268,7 +3453,7 @@
         <v>58922</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -3276,13 +3461,1466 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
       <c r="F19" s="1"/>
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA79F955-C220-4ED8-A426-4D4990E10505}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="23.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="16.81640625" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" customWidth="1"/>
+    <col min="13" max="13" width="36.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3390</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>284</v>
+      </c>
+      <c r="J5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="1">
+        <v>308699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3067</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="1">
+        <v>99183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4151</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L9" s="1">
+        <v>178198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4199</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>34680</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="1">
+        <v>185643</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>284</v>
+      </c>
+      <c r="D17">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="1">
+        <v>308699</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>108</v>
+      </c>
+      <c r="I17" s="1">
+        <v>37</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="1">
+        <v>63734</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C40E21-2707-4F7B-9A25-7F31D2592D7F}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="14.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" customWidth="1"/>
+    <col min="7" max="7" width="16.08984375" customWidth="1"/>
+    <col min="8" max="8" width="17.6328125" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="14.6328125" customWidth="1"/>
+    <col min="13" max="13" width="29.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3277</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>285</v>
+      </c>
+      <c r="J5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" s="1">
+        <v>230247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3257</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3200</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3577</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>4860</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L12" s="1">
+        <v>102101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>285</v>
+      </c>
+      <c r="D17">
+        <v>140</v>
+      </c>
+      <c r="E17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="1">
+        <v>230247</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>118</v>
+      </c>
+      <c r="I17" s="1">
+        <v>45</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" s="1">
+        <v>56757</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6243111-741B-4DF4-964C-8E7F7B251246}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.6328125" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" customWidth="1"/>
+    <col min="9" max="10" width="15.6328125" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" customWidth="1"/>
+    <col min="12" max="12" width="15.6328125" customWidth="1"/>
+    <col min="13" max="13" width="34.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3208</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>295</v>
+      </c>
+      <c r="J5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" s="1">
+        <v>248120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3123</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" s="1">
+        <v>99802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3210</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="1">
+        <v>99960</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3147</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>5241</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="1">
+        <v>101194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>295</v>
+      </c>
+      <c r="D17">
+        <v>132</v>
+      </c>
+      <c r="E17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="1">
+        <v>248120</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>120</v>
+      </c>
+      <c r="I17" s="1">
+        <v>36</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" s="1">
+        <v>58753</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F87A7E-BCB2-473E-8C60-63F960E552E5}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="21.6328125" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" customWidth="1"/>
+    <col min="12" max="12" width="15.26953125" customWidth="1"/>
+    <col min="13" max="13" width="27.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3204</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>130</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="1">
+        <v>235378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3225</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" s="1">
+        <v>99532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3317</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100929</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3133</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3587</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L12" s="1">
+        <v>102188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>286</v>
+      </c>
+      <c r="D17">
+        <v>157</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="1">
+        <v>235378</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>30</v>
+      </c>
+      <c r="I17" s="1">
+        <v>106</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="1">
+        <v>50928</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Experiments/DBCV_DGCNN.xlsx
+++ b/Experiments/DBCV_DGCNN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Documents\GIT\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4973FE3-7D97-432D-A4A4-C477D2D0ED07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1322932-FC2C-45B7-AF81-97292B5C163A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="8" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -882,23 +882,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC741B33-8327-42E5-99D2-10620C98A133}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" customWidth="1"/>
-    <col min="10" max="10" width="16.7265625" customWidth="1"/>
-    <col min="11" max="11" width="12.453125" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" customWidth="1"/>
-    <col min="13" max="13" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -907,21 +907,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -965,7 +965,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -998,7 +998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1012,14 +1012,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -1085,14 +1085,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -1100,7 +1100,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -1133,14 +1133,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1000</v>
       </c>
@@ -1157,14 +1157,14 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
@@ -1189,7 +1189,7 @@
       <c r="I17" s="1"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -1214,7 +1214,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="11" t="s">
         <v>29</v>
@@ -1248,7 +1248,7 @@
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>31</v>
@@ -1281,7 +1281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -1329,27 +1329,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12FA993-8E8A-42F8-A34C-BCBF8AAE8AD1}">
   <dimension ref="A1:P65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" customWidth="1"/>
-    <col min="8" max="8" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" customWidth="1"/>
-    <col min="13" max="13" width="25.81640625" customWidth="1"/>
-    <col min="14" max="14" width="16.453125" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="22.1796875" customWidth="1"/>
+    <col min="16" max="16" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -1358,21 +1358,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1458,14 +1458,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -1521,14 +1521,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -1536,7 +1536,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -1564,14 +1564,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1000</v>
       </c>
@@ -1588,14 +1588,14 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
@@ -1620,7 +1620,7 @@
       <c r="I17" s="1"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1000</v>
       </c>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -1645,7 +1645,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1000</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="11" t="s">
         <v>29</v>
@@ -1679,7 +1679,7 @@
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>31</v>
@@ -1712,7 +1712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="C29" s="1"/>
       <c r="E29" s="1"/>
@@ -1756,21 +1756,21 @@
       </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="C30" s="1"/>
       <c r="E30" s="1"/>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="C31" s="1"/>
       <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2000</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>3596855</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
@@ -1856,14 +1856,14 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="D35" s="3"/>
       <c r="F35" s="1"/>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2000</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>399792</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2000</v>
       </c>
@@ -1919,14 +1919,14 @@
         <v>409159</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="D38" s="3"/>
       <c r="F38" s="1"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="D39" s="3"/>
@@ -1934,7 +1934,7 @@
       <c r="I39" s="3"/>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2000</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>410735</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="9" t="s">
         <v>29</v>
@@ -1979,7 +1979,7 @@
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" t="s">
         <v>31</v>
@@ -2012,7 +2012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>1000</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>604703</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="C49" s="1"/>
       <c r="E49" s="1"/>
@@ -2056,21 +2056,21 @@
       </c>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="C50" s="1"/>
       <c r="E50" s="1"/>
       <c r="G50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="C51" s="1"/>
       <c r="E51" s="1"/>
       <c r="G51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>1</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>5000</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>120280203</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
@@ -2156,14 +2156,14 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="D55" s="3"/>
       <c r="F55" s="1"/>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>5000</v>
       </c>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>5000</v>
       </c>
@@ -2208,14 +2208,14 @@
         <v>2696609</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="D58" s="3"/>
       <c r="F58" s="1"/>
       <c r="I58" s="3"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="D59" s="3"/>
@@ -2223,7 +2223,7 @@
       <c r="I59" s="3"/>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>5000</v>
       </c>
@@ -2232,18 +2232,22 @@
       <c r="F60" s="3">
         <v>2</v>
       </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1">
+        <v>14940</v>
+      </c>
       <c r="H60" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="3">
         <v>175</v>
       </c>
-      <c r="J60" s="1"/>
+      <c r="J60" s="1">
+        <v>201795</v>
+      </c>
       <c r="K60" s="8"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="9" t="s">
         <v>29</v>
@@ -2267,7 +2271,7 @@
       <c r="O63" s="9"/>
       <c r="P63" s="9"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" t="s">
         <v>31</v>
@@ -2315,7 +2319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>1000</v>
       </c>
@@ -2378,24 +2382,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E652DF1D-93D7-4843-A898-B564AEFAAE58}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="16.54296875" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
     <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -2407,21 +2411,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2465,7 +2469,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -2493,7 +2497,7 @@
         <v>240169</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -2507,14 +2511,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -2542,7 +2546,7 @@
         <v>92631</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -2570,14 +2574,14 @@
         <v>103629</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -2585,7 +2589,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -2613,14 +2617,14 @@
         <v>105700</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -2630,7 +2634,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -2647,7 +2651,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -2680,7 +2684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -2715,7 +2719,7 @@
         <v>62288</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -2723,7 +2727,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -2731,7 +2735,7 @@
       <c r="I19" s="1"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="D20" s="1"/>
@@ -2752,24 +2756,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D727ADA0-5113-499F-B7CF-72723C82F907}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.54296875" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15.1796875" customWidth="1"/>
-    <col min="7" max="7" width="21.26953125" customWidth="1"/>
-    <col min="8" max="8" width="15.7265625" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.7265625" customWidth="1"/>
-    <col min="11" max="11" width="15.7265625" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" customWidth="1"/>
-    <col min="13" max="13" width="36.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -2781,21 +2785,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2839,7 +2843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -2867,7 +2871,7 @@
         <v>250010</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -2881,14 +2885,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -2916,7 +2920,7 @@
         <v>104450</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -2944,14 +2948,14 @@
         <v>106311</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -2959,7 +2963,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -2987,14 +2991,14 @@
         <v>103972</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -3004,7 +3008,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -3021,7 +3025,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -3054,7 +3058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -3089,7 +3093,7 @@
         <v>65277</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -3097,7 +3101,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -3118,22 +3122,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C70911A-DBE7-4141-B687-67DF4C8C8D7B}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="3" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
-    <col min="9" max="9" width="18.1796875" customWidth="1"/>
-    <col min="10" max="11" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" customWidth="1"/>
+    <col min="10" max="11" width="17.5703125" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="32.26953125" customWidth="1"/>
+    <col min="13" max="13" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -3145,21 +3149,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3203,7 +3207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -3231,7 +3235,7 @@
         <v>253259</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -3245,14 +3249,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -3280,7 +3284,7 @@
         <v>104248</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -3308,14 +3312,14 @@
         <v>107411</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -3323,7 +3327,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -3351,14 +3355,14 @@
         <v>105169</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -3368,7 +3372,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -3385,7 +3389,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -3418,7 +3422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -3453,7 +3457,7 @@
         <v>58922</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -3461,7 +3465,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -3482,24 +3486,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA79F955-C220-4ED8-A426-4D4990E10505}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="23.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="16.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" customWidth="1"/>
-    <col min="13" max="13" width="36.7265625" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -3511,21 +3515,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3569,7 +3573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -3597,7 +3601,7 @@
         <v>308699</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -3611,14 +3615,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -3646,7 +3650,7 @@
         <v>99183</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -3674,14 +3678,14 @@
         <v>178198</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -3689,7 +3693,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -3717,14 +3721,14 @@
         <v>185643</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -3734,7 +3738,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -3751,7 +3755,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -3784,7 +3788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -3819,7 +3823,7 @@
         <v>63734</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -3827,7 +3831,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -3848,24 +3852,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C40E21-2707-4F7B-9A25-7F31D2592D7F}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" customWidth="1"/>
-    <col min="7" max="7" width="16.08984375" customWidth="1"/>
-    <col min="8" max="8" width="17.6328125" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
-    <col min="13" max="13" width="29.90625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -3877,21 +3881,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3935,7 +3939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -3963,7 +3967,7 @@
         <v>230247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -3977,14 +3981,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -4012,7 +4016,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -4040,14 +4044,14 @@
         <v>100652</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -4055,7 +4059,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -4083,14 +4087,14 @@
         <v>102101</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -4100,7 +4104,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -4117,7 +4121,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -4150,7 +4154,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -4185,7 +4189,7 @@
         <v>56757</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -4193,7 +4197,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -4213,23 +4217,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6243111-741B-4DF4-964C-8E7F7B251246}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6328125" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="14.7265625" customWidth="1"/>
-    <col min="12" max="12" width="15.6328125" customWidth="1"/>
-    <col min="13" max="13" width="34.90625" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" customWidth="1"/>
+    <col min="13" max="13" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -4241,21 +4244,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -4299,7 +4302,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -4327,7 +4330,7 @@
         <v>248120</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -4341,14 +4344,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>99802</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -4404,14 +4407,14 @@
         <v>99960</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -4419,7 +4422,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -4447,14 +4450,14 @@
         <v>101194</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -4464,7 +4467,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -4481,7 +4484,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -4514,7 +4517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -4549,7 +4552,7 @@
         <v>58753</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -4557,7 +4560,7 @@
       <c r="I18" s="1"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
@@ -4577,24 +4580,24 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F87A7E-BCB2-473E-8C60-63F960E552E5}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="10.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
-    <col min="12" max="12" width="15.26953125" customWidth="1"/>
-    <col min="13" max="13" width="27.81640625" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="C1" s="1"/>
       <c r="E1" s="1"/>
@@ -4606,21 +4609,21 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -4664,7 +4667,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1000</v>
       </c>
@@ -4692,7 +4695,7 @@
         <v>235378</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -4706,14 +4709,14 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="F7" s="1"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1000</v>
       </c>
@@ -4741,7 +4744,7 @@
         <v>99532</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1000</v>
       </c>
@@ -4769,14 +4772,14 @@
         <v>100929</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="F10" s="1"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -4784,7 +4787,7 @@
       <c r="I11" s="3"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1000</v>
       </c>
@@ -4812,14 +4815,14 @@
         <v>102188</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
@@ -4829,7 +4832,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
         <v>29</v>
@@ -4846,7 +4849,7 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>31</v>
@@ -4879,7 +4882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1000</v>
       </c>
@@ -4914,7 +4917,7 @@
         <v>50928</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
@@ -4928,5 +4931,6 @@
     <mergeCell ref="G15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Experiments/DBCV_DGCNN.xlsx
+++ b/Experiments/DBCV_DGCNN.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\das-sb\Documents\GIT\thesis_documentation\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1322932-FC2C-45B7-AF81-97292B5C163A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF676C3-75F9-450B-A9FD-3CEABE4992F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{011C6E85-EDD6-4ED4-BC54-083128C36B70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="149">
   <si>
     <t>TEST DATASET(1024)</t>
   </si>
@@ -455,6 +456,42 @@
   </si>
   <si>
     <t>-0.100</t>
+  </si>
+  <si>
+    <t>Average Similarity</t>
+  </si>
+  <si>
+    <t>Dataset Size(rep Objs)</t>
+  </si>
+  <si>
+    <t># rep Objs</t>
+  </si>
+  <si>
+    <t>Dataset Size(test)</t>
+  </si>
+  <si>
+    <t>Distance Metric</t>
+  </si>
+  <si>
+    <t>Average Dist</t>
+  </si>
+  <si>
+    <t>agglomerative</t>
+  </si>
+  <si>
+    <t>Hausdorff</t>
+  </si>
+  <si>
+    <t>multi-hdbscan</t>
+  </si>
+  <si>
+    <t>0.170</t>
+  </si>
+  <si>
+    <t>kmedoids</t>
+  </si>
+  <si>
+    <t>spectral</t>
   </si>
 </sst>
 </file>
@@ -1326,6 +1363,364 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F87A7E-BCB2-473E-8C60-63F960E552E5}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3204</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
+        <v>286</v>
+      </c>
+      <c r="J5" t="s">
+        <v>130</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="1">
+        <v>235378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3225</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" s="1">
+        <v>99532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3317</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100929</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3133</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
+        <v>175</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3587</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L12" s="1">
+        <v>102188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>286</v>
+      </c>
+      <c r="D17">
+        <v>157</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="1">
+        <v>235378</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>30</v>
+      </c>
+      <c r="I17" s="1">
+        <v>106</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="1">
+        <v>50928</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12FA993-8E8A-42F8-A34C-BCBF8AAE8AD1}">
   <dimension ref="A1:P65"/>
@@ -2380,6 +2775,123 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7B41AB-0167-4B72-8483-B671B61D35D1}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>949647</v>
+      </c>
+      <c r="B3">
+        <v>175</v>
+      </c>
+      <c r="C3">
+        <v>49981</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>949647</v>
+      </c>
+      <c r="B4">
+        <v>95</v>
+      </c>
+      <c r="C4">
+        <v>49981</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>949647</v>
+      </c>
+      <c r="B5">
+        <v>175</v>
+      </c>
+      <c r="C5">
+        <v>49981</v>
+      </c>
+      <c r="D5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>949647</v>
+      </c>
+      <c r="B6">
+        <v>175</v>
+      </c>
+      <c r="C6">
+        <v>49981</v>
+      </c>
+      <c r="D6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E652DF1D-93D7-4843-A898-B564AEFAAE58}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2753,7 +3265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D727ADA0-5113-499F-B7CF-72723C82F907}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3119,7 +3631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C70911A-DBE7-4141-B687-67DF4C8C8D7B}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3483,7 +3995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA79F955-C220-4ED8-A426-4D4990E10505}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3849,7 +4361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C40E21-2707-4F7B-9A25-7F31D2592D7F}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4214,7 +4726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6243111-741B-4DF4-964C-8E7F7B251246}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4575,362 +5087,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F87A7E-BCB2-473E-8C60-63F960E552E5}">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" customWidth="1"/>
-    <col min="13" max="13" width="27.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="D5" s="1"/>
-      <c r="F5" s="3">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3204</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="3">
-        <v>286</v>
-      </c>
-      <c r="J5" t="s">
-        <v>130</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="1">
-        <v>235378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="F7" s="1"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="D8" s="1"/>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3225</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="3">
-        <v>175</v>
-      </c>
-      <c r="J8" t="s">
-        <v>135</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="L8" s="1">
-        <v>99532</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="D9" s="1"/>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>3317</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="3">
-        <v>175</v>
-      </c>
-      <c r="J9" t="s">
-        <v>132</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="L9" s="1">
-        <v>100929</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="F10" s="1"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="F11" s="1"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="D12" s="1"/>
-      <c r="F12" s="3">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>3133</v>
-      </c>
-      <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="3">
-        <v>175</v>
-      </c>
-      <c r="J12" s="1">
-        <v>3587</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="L12" s="1">
-        <v>102188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>1000</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3">
-        <v>286</v>
-      </c>
-      <c r="D17">
-        <v>157</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="1">
-        <v>235378</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="1">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1">
-        <v>106</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="K17" s="1">
-        <v>50928</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="K18" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:K15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>